--- a/XC_two_wise_result.xlsx
+++ b/XC_two_wise_result.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -593,22 +593,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>44915</v>
+        <v>44914</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -621,27 +621,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
         <v>44915</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -654,24 +656,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>44913</v>
+        <v>44916</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -679,29 +679,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>44916</v>
+        <v>44912</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -709,29 +707,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
       <c r="D10" s="2" t="n">
-        <v>44916</v>
+        <v>44915</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -744,22 +740,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>44912</v>
+        <v>44917</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -772,23 +770,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>44914</v>
+        <v>44918</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -797,28 +795,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
       <c r="D13" s="2" t="n">
-        <v>44917</v>
+        <v>44913</v>
       </c>
       <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -832,23 +830,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>44917</v>
+        <v>44915</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +855,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>44913</v>
+        <v>44912</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -892,22 +890,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>44917</v>
+        <v>44916</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -915,29 +915,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>广州</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
       <c r="D17" s="2" t="n">
-        <v>44915</v>
+        <v>44918</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -945,25 +943,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>44918</v>
+        <v>44917</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -978,17 +976,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>44914</v>
+        <v>44913</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
@@ -1003,28 +1001,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>44912</v>
+        <v>44917</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1033,29 +1031,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>44912</v>
+        <v>44914</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1063,28 +1059,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>44918</v>
+        <v>44912</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1093,16 +1089,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
       <c r="D23" s="2" t="n">
-        <v>44917</v>
+        <v>44913</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
@@ -1126,22 +1122,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>44916</v>
+        <v>44918</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1149,7 +1147,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1161,17 +1159,15 @@
         <v>44913</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1179,28 +1175,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>44915</v>
+        <v>44914</v>
       </c>
       <c r="E26" t="n">
         <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1209,28 +1205,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>44918</v>
+        <v>44914</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
         <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1239,28 +1235,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>44913</v>
+        <v>44915</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
         <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1274,20 +1270,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>44914</v>
+        <v>44916</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1297,12 +1293,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1312,13 +1308,13 @@
         <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1332,23 +1328,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>44918</v>
+        <v>44915</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1357,28 +1353,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>44918</v>
+        <v>44917</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1387,7 +1383,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1396,19 +1392,19 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1417,7 +1413,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1426,16 +1422,16 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
         <v>2</v>
@@ -1447,28 +1443,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>44917</v>
+        <v>44913</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1477,28 +1473,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>44914</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1507,28 +1503,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
       <c r="D37" s="2" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1537,19 +1533,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>44918</v>
+        <v>44916</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
         <v>3</v>
@@ -1558,7 +1554,7 @@
         <v>6</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1567,28 +1563,534 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>44916</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>44916</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>44918</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>44913</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>44916</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>44916</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>44913</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>44913</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>44917</v>
+      </c>
+      <c r="E48" t="n">
+        <v>7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>44918</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>44914</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>44916</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>44914</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>44918</v>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>44915</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
-        <v>44915</v>
-      </c>
-      <c r="E39" t="n">
-        <v>6</v>
-      </c>
-      <c r="F39" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>44917</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
